--- a/编程/数据集/常驻人口，出生率，死亡率，自然增长率，城镇化率.xlsx
+++ b/编程/数据集/常驻人口，出生率，死亡率，自然增长率，城镇化率.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\羽\Desktop\数模\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\Mm\编程\数据集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6386D5-747E-4047-9BF5-B1BAB03A739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B50A5C-4C19-4292-9F5A-0AE99C457FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4910" yWindow="4620" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -400,22 +400,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.08203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
     <col min="12" max="13" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,27 +444,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2013</v>
+      </c>
+      <c r="B2">
+        <v>2668</v>
+      </c>
+      <c r="G2">
+        <v>7.74</v>
+      </c>
+      <c r="H2" s="1">
+        <v>5.17</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2.57</v>
+      </c>
+      <c r="J2" s="1">
+        <v>55.74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B3">
-        <v>2668</v>
+        <v>2642</v>
       </c>
       <c r="G3">
-        <v>7.74</v>
-      </c>
-      <c r="H3" s="1">
-        <v>5.17</v>
-      </c>
-      <c r="I3" s="1">
-        <v>2.57</v>
-      </c>
-      <c r="J3" s="1">
-        <v>55.74</v>
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H3">
+        <v>6.45</v>
+      </c>
+      <c r="I3">
+        <v>1.58</v>
+      </c>
+      <c r="J3">
+        <v>56.81</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -474,212 +491,192 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B4">
-        <v>2642</v>
+        <v>2613</v>
       </c>
       <c r="G4">
-        <v>8.0299999999999994</v>
+        <v>6.2</v>
       </c>
       <c r="H4">
-        <v>6.45</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
-        <v>1.58</v>
+        <v>0.4</v>
       </c>
       <c r="J4">
-        <v>56.81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+        <v>57.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B5">
-        <v>2613</v>
+        <v>2567</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>7.45</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="I5">
-        <v>0.4</v>
+        <v>1.49</v>
       </c>
       <c r="J5">
-        <v>57.64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B6">
-        <v>2567</v>
+        <v>2526</v>
       </c>
       <c r="G6">
-        <v>7.45</v>
+        <v>7.13</v>
       </c>
       <c r="H6">
-        <v>5.95</v>
+        <v>6.97</v>
       </c>
       <c r="I6">
-        <v>1.49</v>
+        <v>0.15</v>
       </c>
       <c r="J6">
-        <v>58.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>59.71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B7">
-        <v>2526</v>
+        <v>2484</v>
       </c>
       <c r="G7">
-        <v>7.13</v>
+        <v>6.35</v>
       </c>
       <c r="H7">
-        <v>6.97</v>
+        <v>6.79</v>
       </c>
       <c r="I7">
-        <v>0.15</v>
+        <v>-0.44</v>
       </c>
       <c r="J7">
-        <v>59.71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>60.85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8">
-        <v>2484</v>
+        <v>2448</v>
       </c>
       <c r="G8">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="H8">
-        <v>6.79</v>
+        <v>7.55</v>
       </c>
       <c r="I8">
-        <v>-0.44</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="J8">
-        <v>60.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>61.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B9">
-        <v>2448</v>
+        <v>2399</v>
+      </c>
+      <c r="D9">
+        <v>189.47</v>
+      </c>
+      <c r="E9">
+        <v>62.71</v>
+      </c>
+      <c r="F9">
+        <v>104.89</v>
       </c>
       <c r="G9">
-        <v>6.39</v>
+        <v>4.84</v>
       </c>
       <c r="H9">
-        <v>7.55</v>
+        <v>7.81</v>
       </c>
       <c r="I9">
-        <v>-1.1599999999999999</v>
+        <v>-2.97</v>
       </c>
       <c r="J9">
-        <v>61.63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>62.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B10">
-        <v>2399</v>
-      </c>
-      <c r="D10">
-        <v>189.47</v>
-      </c>
-      <c r="E10">
-        <v>62.71</v>
-      </c>
-      <c r="F10">
-        <v>104.89</v>
+        <v>2375</v>
       </c>
       <c r="G10">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>7.81</v>
+        <v>8.08</v>
       </c>
       <c r="I10">
-        <v>-2.97</v>
+        <v>-3.38</v>
       </c>
       <c r="J10">
-        <v>62.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>63.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B11">
-        <v>2375</v>
+        <v>2348</v>
       </c>
       <c r="G11">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="H11">
-        <v>8.08</v>
+        <v>8.4</v>
       </c>
       <c r="I11">
-        <v>-3.38</v>
+        <v>-4.07</v>
       </c>
       <c r="J11">
-        <v>63.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>63.73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B12">
-        <v>2348</v>
+        <v>2339</v>
       </c>
       <c r="G12">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="H12">
-        <v>8.4</v>
+        <v>9.16</v>
       </c>
       <c r="I12">
-        <v>-4.07</v>
+        <v>-5.39</v>
       </c>
       <c r="J12">
-        <v>63.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2023</v>
-      </c>
-      <c r="B13">
-        <v>2339</v>
-      </c>
-      <c r="G13">
-        <v>3.77</v>
-      </c>
-      <c r="H13">
-        <v>9.16</v>
-      </c>
-      <c r="I13">
-        <v>-5.39</v>
-      </c>
-      <c r="J13">
         <v>64.72</v>
       </c>
     </row>
